--- a/ci-cd-merge-resolver/repoCollector/datasets/nifi.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/nifi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -51,6 +51,78 @@
   </si>
   <si>
     <t>e42ea9ad457c5b5a1d2da5fa3d3494aacb0cb8d4</t>
+  </si>
+  <si>
+    <t>0636f0e731cd28299edd3a6e9db90de5045ab662</t>
+  </si>
+  <si>
+    <t>8e2308b78de480dd7848ffe8efb485a5ee61c42a</t>
+  </si>
+  <si>
+    <t>d63cd6bd2f9adc3dfc4c7fe168e38081a5b13564</t>
+  </si>
+  <si>
+    <t>ef80549d63a5dc347731701d32a80c2446c46523</t>
+  </si>
+  <si>
+    <t>171b9c4e94113dc6e3c42154eb500e046620249e</t>
+  </si>
+  <si>
+    <t>012680020173a2e3db2df2f7a1cb633bf356c2f0</t>
+  </si>
+  <si>
+    <t>b974445ddd38ec7e84995225b86987e6af1af52c</t>
+  </si>
+  <si>
+    <t>5ecdb1858e94938cd426b12bc48d3725109c6e96</t>
+  </si>
+  <si>
+    <t>2215bc848b7db395b2ca9ac7cc4dc10891393721</t>
+  </si>
+  <si>
+    <t>7a3e3efce1071c60ae90fde65be4ec92dbccf66c</t>
+  </si>
+  <si>
+    <t>d2a969e3d63689624f7482a11fe57ece19147e4f</t>
+  </si>
+  <si>
+    <t>57dadb7286c49d035df83ac565b0d72817469ba4</t>
+  </si>
+  <si>
+    <t>4df65121263fe9b3e488f81ce50d8f96e3643c21</t>
+  </si>
+  <si>
+    <t>498b5023ce4f99e67184f399de740b142fca510d</t>
+  </si>
+  <si>
+    <t>16f185245309ac3bcf9629b1c4d4dc655f18ca68</t>
+  </si>
+  <si>
+    <t>c59087bc3aeea240a344531e6be0166a25d0d753</t>
+  </si>
+  <si>
+    <t>fd35b8ffd7d4a66ef149c1bd1341dfee3ede80c7</t>
+  </si>
+  <si>
+    <t>07c619cf40affef136e61f87d2075853e392bfc3</t>
+  </si>
+  <si>
+    <t>f6ec437bc79b42eb516429381f117a9dd20050d3</t>
+  </si>
+  <si>
+    <t>d696391f76cb14bf4bdaedb4e88d129aa2e54dc2</t>
+  </si>
+  <si>
+    <t>0d7edcb3ace95e8729c4bc27457d702fdd879f09</t>
+  </si>
+  <si>
+    <t>e4cebba3c7868010c2b9fd994b850f40b81aa044</t>
+  </si>
+  <si>
+    <t>5a04021dd7a61cc7c76b24405288713116bcd682</t>
+  </si>
+  <si>
+    <t>a549621267c6517c4774579c3d95f0d7a0c1f68b</t>
   </si>
 </sst>
 </file>
@@ -95,7 +167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,7 +213,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>34.0</v>
+        <v>67.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>8.0</v>
@@ -156,10 +228,266 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.034999992698431015</v>
+        <v>0.9610000252723694</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>139.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>11.984000205993652</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>12.399001121520996</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>139.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>13.269999504089355</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>139.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>13.00500202178955</v>
+      </c>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>11.668999671936035</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>139.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>12.476999282836914</v>
+      </c>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>139.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>12.055999755859375</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>139.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>12.214001655578613</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
